--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.69366045605857</v>
+        <v>10.35021982410952</v>
       </c>
       <c r="D2" t="n">
-        <v>27.05213677601045</v>
+        <v>4.395972226101698</v>
       </c>
       <c r="E2" t="n">
-        <v>22.86489585597801</v>
+        <v>3.715545576596427</v>
       </c>
       <c r="F2" t="n">
-        <v>13.00005964244631</v>
+        <v>2.112509691897525</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.86421634685522</v>
+        <v>11.35293515636397</v>
       </c>
       <c r="D3" t="n">
-        <v>30.93227368874709</v>
+        <v>5.026494474421402</v>
       </c>
       <c r="E3" t="n">
-        <v>22.86489585597801</v>
+        <v>3.715545576596427</v>
       </c>
       <c r="F3" t="n">
-        <v>13.00005964244631</v>
+        <v>2.112509691897525</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.06333183868124</v>
+        <v>7.810291423785702</v>
       </c>
       <c r="D4" t="n">
-        <v>47.11289632361823</v>
+        <v>7.655845652587963</v>
       </c>
       <c r="E4" t="n">
-        <v>22.86489585597801</v>
+        <v>3.715545576596427</v>
       </c>
       <c r="F4" t="n">
-        <v>13.00005964244631</v>
+        <v>2.112509691897525</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.14917249748383</v>
+        <v>3.599240530841122</v>
       </c>
       <c r="D5" t="n">
-        <v>13.51793821687008</v>
+        <v>2.196664960241388</v>
       </c>
       <c r="E5" t="n">
-        <v>22.86489585597801</v>
+        <v>3.715545576596427</v>
       </c>
       <c r="F5" t="n">
-        <v>13.00005964244631</v>
+        <v>2.112509691897525</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.31860393949044</v>
+        <v>1.839273140167197</v>
       </c>
       <c r="D6" t="n">
-        <v>11.23444212833449</v>
+        <v>1.825596845854355</v>
       </c>
       <c r="E6" t="n">
-        <v>22.86489585597801</v>
+        <v>3.715545576596427</v>
       </c>
       <c r="F6" t="n">
-        <v>13.00005964244631</v>
+        <v>2.112509691897525</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
